--- a/04_DESIGN_TABLES/DesignTable_6408.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6408.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -547,6 +547,21 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>SOCKAF@SOCKET</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>HEADDIA@REF</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -590,7 +605,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -600,7 +615,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: Air-Way lists only a solid plug at this size -&gt; OMi 6408-02-O built solid (OMi does not say hollow/solid here; ASSUMPTION)</t>
+          <t>BUILD 2026-09-25: Air-Way lists only a solid plug at this size -&gt; OMi 6408-02-O built solid (OMi does not say hollow/solid here; ASSUMPTION) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=0.6~0.600; HEXB@HEX=0.44~0.438</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -656,7 +671,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -666,7 +681,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: Air-Way lists only a solid plug at this size -&gt; OMi 6408-03-O built solid (OMi does not say hollow/solid here; ASSUMPTION)</t>
+          <t>BUILD 2026-09-25: Air-Way lists only a solid plug at this size -&gt; OMi 6408-03-O built solid (OMi does not say hollow/solid here; ASSUMPTION) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=0.6~0.600; HEXB@HEX=0.5~0.500</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -722,7 +737,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -732,7 +747,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>BUILD: OMi 6408-04-O-SLD (External Hex Plug Solid)</t>
+          <t>BUILD: OMi 6408-04-O-SLD (External Hex Plug Solid) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=0.67~0.670; HEXB@HEX=0.56~0.562</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -790,7 +805,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -800,7 +815,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 6408-04-O = the cored plug (OMi sells the solid one separately as 6408-04-O-SLD; Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) - was DROP (no SKU match); replaces the Air-Way-less placeholder row 6408-04-O</t>
+          <t>BUILD 2026-09-25: OMi 6408-04-O = the cored plug (OMi sells the solid one separately as 6408-04-O-SLD; Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) - was DROP (no SKU match); replaces the Air-Way-less placeholder row 6408-04-O | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=0.67~0.670; HEXB@HEX=0.56~0.562; HOLE@BORE=0.2~0.205</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -856,7 +871,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -866,7 +881,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: Air-Way lists only a solid plug at this size -&gt; OMi 6408-05-O built solid (OMi does not say hollow/solid here; ASSUMPTION)</t>
+          <t>BUILD 2026-09-25: Air-Way lists only a solid plug at this size -&gt; OMi 6408-05-O built solid (OMi does not say hollow/solid here; ASSUMPTION) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=0.67~0.670; HEXB@HEX=0.63~0.625</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1372,7 +1387,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1382,7 +1397,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 6408-12-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored)</t>
+          <t>BUILD 2026-09-25: OMi 6408-12-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=1.09~1.090; HEXB@HEX=1.25~1.250; HOLE@BORE=0.66~0.656</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1497,7 +1512,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -1507,7 +1522,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>ORB -14 groove width unmeasured | BUILD 2026-09-25: OMi 6408-14-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored)</t>
+          <t>ORB -14 groove width unmeasured | BUILD 2026-09-25: OMi 6408-14-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=1.09~1.090; HEXB@HEX=1.38~1.375; HOLE@BORE=0.72~0.718</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -1765,7 +1780,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 6408-20-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored)</t>
+          <t>BUILD 2026-09-25: OMi 6408-20-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=1.2~1.200; HEXB@HEX=1.88~1.875; HOLE@BORE=1.09~1.093</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -1884,7 +1899,7 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -1894,7 +1909,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 6408-24-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored)</t>
+          <t>BUILD 2026-09-25: OMi 6408-24-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=1.27~1.270; HEXB@HEX=2.13~2.125; HOLE@BORE=1.34~1.344</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2009,7 +2024,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -2019,7 +2034,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>ORB -32 groove width unmeasured | BUILD 2026-09-25: OMi 6408-32-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored)</t>
+          <t>ORB -32 groove width unmeasured | BUILD 2026-09-25: OMi 6408-32-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L@DRIVE=1.43~1.430; HEXB@HEX=2.75~2.75; HOLE@BORE=1.81~1.813</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2224,24 +2239,32 @@
           <t>6408-HHP-08-O</t>
         </is>
       </c>
+      <c r="B31" t="n">
+        <v>0.58</v>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>6408-HHP-08-O</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>3/4-16 (ORB)</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p.67 table TFA-p067-t05 "6408-H-O MORB HOLLOW HEX PLUG" row 6408-H08-O (= OMi 6408-HHP-08-O) col "L LGTH" = "0.58" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 445.8, page verified True) [Brennan = yes 2026-10-18] - overall length; SOCKAF@SOCKET: Brennan TFA catalog p.67 table TFA-p067-t05 "6408-H-O MORB HOLLOW HEX PLUG" row 6408-H08-O (= OMi 6408-HHP-08-O) col "C5 HEX" = "0.313" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 445.8, page verified True) [Brennan = yes 2026-10-18] - socket across flats [column not in today's base table: add it]; $PRP@EndA_Thread: OMi WebsitePartsInfo2026.xlsx Items!U1828 (Side 1 Thread "3/4-16 UNF"); format of the table's 6408 rows; HEADDIA@REF: own Brennan STEP 09_STEP_FILES/BRENNAN_6408-H08-O.stp (sha256 6562c84d1d96c1c9...), tools/_out/newmasters_20261002/work/PLUGS/evidence/measure/plugs_measure_v3.jsonl (tools/measure/plugs.py): head.head_dia = 0.875 (round head dia; STEP L 0.58 = catalog L, socket 0.313 = catalog C5) [Brennan = yes 2026-10-18] [column not in today's base table: add it]</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2253,6 +2276,17 @@
         <is>
           <t>6408-HHP-08-O</t>
         </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.875</v>
       </c>
     </row>
     <row r="32">

--- a/04_DESIGN_TABLES/DesignTable_6408.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6408.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1622,7 +1622,7 @@
         <v>0.125</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.874</v>
+        <v>0.88</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>ORB end: sourced (SAE J1926-4 plug); L/hex: Air-Way single source; HOLE@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1819 Side 1 ID = 0.874 (table had 0.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>ORB end: sourced (SAE J1926-4 plug); L/hex: Air-Way single source; HOLE@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1819 Side 1 ID = 0.874 (table had 0.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; HOLE@BORE: Air-Way 0.88 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.874) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>BUILD 2026-09-25: OMi 6408-16-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored)</t>
+          <t>BUILD 2026-09-25: OMi 6408-16-O = the cored (hollow) plug (Brennan 6408-08-O / 6408-20-O STEPs of the same part numbers are cored) | 2026-10-20 Air-Way first: HOLE@BORE OMi/Brennan 0.874 -&gt; Air-Way 0.88</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
